--- a/htr-modele-metier-imagerie/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/htr-modele-metier-imagerie/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:11:30+00:00</t>
+    <t>2025-10-14T08:46:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
